--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486886_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486886_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.308400000000001</v>
+        <v>8.635400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.175</v>
+        <v>7.6205</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1334</v>
+        <v>1.0149</v>
       </c>
       <c r="G2" t="n">
         <v>3.9264</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1767</v>
+        <v>0.5037</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4806</v>
+        <v>-0.0351</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6573</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.3573</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6708</v>
+        <v>2.9559</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3148</v>
+        <v>3.6296</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.644</v>
+        <v>-0.6737</v>
       </c>
       <c r="G3" t="n">
         <v>3.6346</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6379</v>
+        <v>0.923</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9717</v>
+        <v>0.2865</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6662</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-1.3963</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8029</v>
+        <v>2.8182</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2415</v>
+        <v>5.4347</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5614</v>
+        <v>-2.6166</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3525</v>
+        <v>4.8655</v>
       </c>
       <c r="H4" t="n">
-        <v>2.076</v>
+        <v>-0.4467</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7235</v>
+        <v>5.3122</v>
       </c>
       <c r="J4" t="n">
-        <v>1.667</v>
+        <v>7.1241</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6012</v>
+        <v>2.4411</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9342</v>
+        <v>4.683</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3144</v>
+        <v>-2.2586</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5252</v>
+        <v>-2.8878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2107</v>
+        <v>0.6291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9308</v>
+        <v>-0.5114</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9881</v>
+        <v>-0.6627</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9189</v>
+        <v>0.1513</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1088</v>
+        <v>-2.3573</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7418</v>
+        <v>1.4572</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7141</v>
+        <v>0.7258</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9723</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8655</v>
+        <v>0.3525</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4467</v>
+        <v>2.076</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3122</v>
+        <v>-1.7235</v>
       </c>
       <c r="J5" t="n">
-        <v>7.1241</v>
+        <v>1.667</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4411</v>
+        <v>3.6012</v>
       </c>
       <c r="L5" t="n">
-        <v>4.683</v>
+        <v>-1.9342</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2586</v>
+        <v>-1.3144</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.8878</v>
+        <v>-1.5252</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6291</v>
+        <v>0.2107</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5878</v>
+        <v>0.5851</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3833</v>
+        <v>-0.5038</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2045</v>
+        <v>1.0889</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3573</v>
+        <v>0.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2837</v>
+        <v>0.7755</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4992</v>
+        <v>0.3171</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7845</v>
+        <v>0.4584</v>
       </c>
       <c r="G6" t="n">
         <v>0.5401</v>
@@ -922,13 +922,13 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3677</v>
+        <v>-0.1404</v>
       </c>
       <c r="T6" t="n">
-        <v>0.244</v>
+        <v>0.0619</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1238</v>
+        <v>-0.2023</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0239</v>
+        <v>0.7403</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3483</v>
+        <v>0.2678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3244</v>
+        <v>0.4726</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4094</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8466</v>
+        <v>-0.0823</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7169</v>
+        <v>-0.1008</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1297</v>
+        <v>0.0185</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7587</v>
+        <v>-1.2761</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9427</v>
+        <v>-0.6677</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8159</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0097</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1596</v>
+        <v>-0.677</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4611</v>
+        <v>-0.186</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6985</v>
+        <v>-0.491</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.15</v>
+        <v>-1.8623</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1463</v>
+        <v>-1.2806</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0038</v>
+        <v>-0.5817</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7551</v>
+        <v>-2.1573</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3682</v>
+        <v>-1.8492</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6131</v>
+        <v>-0.3081</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2437</v>
+        <v>-1.3502</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2039</v>
+        <v>-0.6</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0398</v>
+        <v>-0.7502</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5114</v>
+        <v>-0.8071</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1643</v>
+        <v>-1.2492</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6529</v>
+        <v>0.4422</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.256</v>
+        <v>-0.1424</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1509</v>
+        <v>0.0696</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1051</v>
+        <v>-0.2121</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7246</v>
+        <v>-2.006</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9354</v>
+        <v>-2.3283</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7892</v>
+        <v>0.3223</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1573</v>
+        <v>-1.7551</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8492</v>
+        <v>-2.3682</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3081</v>
+        <v>0.6131</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3502</v>
+        <v>-0.2437</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6</v>
+        <v>-0.2039</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7502</v>
+        <v>-0.0398</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8071</v>
+        <v>-1.5114</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2492</v>
+        <v>-2.1643</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4422</v>
+        <v>0.6529</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0047</v>
+        <v>0.4</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5851</v>
+        <v>-0.0312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4196</v>
+        <v>0.4312</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0971</v>
+        <v>-2.8673</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0689</v>
+        <v>-1.8985</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0281</v>
+        <v>-0.9688</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4624</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4293</v>
+        <v>-0.1995</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3294</v>
+        <v>-0.1589</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.0533</v>
+        <v>9.370800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.503</v>
+        <v>11.8204</v>
       </c>
       <c r="F12" t="n">
         <v>-2.4496</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5252</v>
+        <v>6.525199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-1.946499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4716</v>
+        <v>8.471599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>17.5391</v>
@@ -1381,7 +1381,7 @@
         <v>5.356699999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>5.133700000000001</v>
+        <v>5.1337</v>
       </c>
       <c r="Q12" t="n">
         <v>-7.1869</v>
@@ -1390,13 +1390,13 @@
         <v>12.3206</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6588999999999998</v>
+        <v>0.6587999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5779</v>
+        <v>-1.2605</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9191</v>
+        <v>1.9192</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9465</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1976</v>
+        <v>1.5281</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7788</v>
+        <v>0.465</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4189</v>
+        <v>1.0632</v>
       </c>
       <c r="G13" t="n">
         <v>1.6435</v>
@@ -1468,13 +1468,13 @@
         <v>0.2053</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6773</v>
+        <v>0.0078</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2362</v>
+        <v>-0.0776</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4411</v>
+        <v>0.0854</v>
       </c>
       <c r="V13" t="n">
         <v>0.6982</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1624</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0584</v>
+        <v>0.2676</v>
       </c>
       <c r="F14" t="n">
-        <v>0.104</v>
+        <v>0.2732</v>
       </c>
       <c r="G14" t="n">
         <v>0.2822</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1197</v>
+        <v>0.2586</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.2092</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1197</v>
+        <v>0.0494</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0505</v>
+        <v>0.1395</v>
       </c>
       <c r="E15" t="n">
         <v>-0.0539</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1044</v>
+        <v>0.1933</v>
       </c>
       <c r="G15" t="n">
         <v>-0.008800000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1461</v>
+        <v>-0.0571</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0143</v>
+        <v>0.0746</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0137</v>
+        <v>-0.0356</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.4329</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9142</v>
+        <v>-0.4685</v>
       </c>
       <c r="G16" t="n">
-        <v>0.124</v>
+        <v>0.9581</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0026</v>
+        <v>1.8394</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8786</v>
+        <v>-0.8813</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6432</v>
+        <v>1.5023</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2221</v>
+        <v>2.1996</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.579</v>
+        <v>-0.6974</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5192</v>
+        <v>-0.5441</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2195</v>
+        <v>-0.3602</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2996</v>
+        <v>-0.1839</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4908</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1321</v>
+        <v>-0.1724</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1431</v>
+        <v>-0.0427</v>
       </c>
       <c r="U16" t="n">
-        <v>0.989</v>
+        <v>-0.1297</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2484</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2484</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7714</v>
+        <v>-0.0411</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0145</v>
+        <v>1.2458</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-1.2869</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9581</v>
+        <v>-1.8028</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8394</v>
+        <v>-1.3108</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8813</v>
+        <v>-0.492</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5023</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1996</v>
+        <v>1.0191</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6974</v>
+        <v>-0.0529</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5441</v>
+        <v>-2.769</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3602</v>
+        <v>-2.3299</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1839</v>
+        <v>-0.4391</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9081</v>
+        <v>-0.4436</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4611</v>
+        <v>-0.899</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.447</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.5927</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8274</v>
+        <v>1.571</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7019</v>
+        <v>-2.1638</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8028</v>
+        <v>-1.4533</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3108</v>
+        <v>-1.5637</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.492</v>
+        <v>0.1104</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.8261</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0191</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0529</v>
+        <v>0.9204</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.769</v>
+        <v>-3.2794</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3299</v>
+        <v>-2.4694</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4391</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.277</v>
+        <v>-0.4145</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3174</v>
+        <v>-0.8874</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0404</v>
+        <v>0.4729</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>1.0698</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>1.6591</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0103</v>
+        <v>-0.6419</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0584</v>
+        <v>0.5094</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0687</v>
+        <v>-1.1513</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6655</v>
+        <v>0.124</v>
       </c>
       <c r="H19" t="n">
-        <v>1.418</v>
+        <v>1.0026</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2475</v>
+        <v>-0.8786</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5111</v>
+        <v>2.6432</v>
       </c>
       <c r="K19" t="n">
-        <v>3.498</v>
+        <v>3.2221</v>
       </c>
       <c r="L19" t="n">
-        <v>0.013</v>
+        <v>-0.579</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8456</v>
+        <v>-2.5192</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.08</v>
+        <v>-2.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2345</v>
+        <v>-0.2996</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6427</v>
+        <v>-3.4908</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-4.1068</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7348</v>
+        <v>0.4766</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0381</v>
+        <v>-0.2753</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3033</v>
+        <v>0.7518</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7679</v>
+        <v>2.2484</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5893</v>
+        <v>2.2484</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0519</v>
+        <v>-0.8899</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0723</v>
+        <v>1.5353</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1242</v>
+        <v>-2.4253</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0236</v>
+        <v>1.6655</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1919</v>
+        <v>1.418</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1682</v>
+        <v>0.2475</v>
       </c>
       <c r="J20" t="n">
-        <v>0.731</v>
+        <v>3.5111</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6916</v>
+        <v>3.498</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.013</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7074</v>
+        <v>-1.8456</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4997</v>
+        <v>-2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2077</v>
+        <v>0.2345</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.616</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.37</v>
+        <v>0.8552</v>
       </c>
       <c r="T20" t="n">
-        <v>0.368</v>
+        <v>0.5151</v>
       </c>
       <c r="U20" t="n">
-        <v>0.002</v>
+        <v>0.3401</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8295</v>
+        <v>-1.7679</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8295</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2204</v>
+        <v>-1.1653</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9434</v>
+        <v>-0.0323</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1638</v>
+        <v>-1.1329</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4533</v>
+        <v>0.0236</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5637</v>
+        <v>0.1919</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1104</v>
+        <v>-0.1682</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8261</v>
+        <v>0.731</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.6916</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9204</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2794</v>
+        <v>-0.7074</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4694</v>
+        <v>-0.4997</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.2077</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0422</v>
+        <v>0.2567</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5151</v>
+        <v>0.2634</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4729</v>
+        <v>-0.0067</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0698</v>
+        <v>-0.8295</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5893</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3278</v>
+        <v>-1.3086</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1469</v>
+        <v>-1.3561</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1809</v>
+        <v>0.0475</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8757</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1988</v>
+        <v>0.2179</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0931</v>
+        <v>-0.3023</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2919</v>
+        <v>0.5203</v>
       </c>
       <c r="V22" t="n">
         <v>0.3491</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4519</v>
+        <v>-2.3603</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9742</v>
+        <v>-1.4972</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4777</v>
+        <v>-0.863</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6591</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5912</v>
+        <v>0.6828</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6701</v>
+        <v>0.1471</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9211</v>
+        <v>0.5357</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7695</v>
+        <v>-2.5289</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0563</v>
+        <v>-0.6378</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7132</v>
+        <v>-1.8911</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4224</v>
@@ -2326,13 +2326,13 @@
         <v>0.2053</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5524</v>
+        <v>-0.3119</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8563</v>
+        <v>-0.4379</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3039</v>
+        <v>0.126</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.0535</v>
+        <v>-7.3559</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4498</v>
+        <v>2.4497</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.5031</v>
+        <v>-9.8056</v>
       </c>
       <c r="G25" t="n">
         <v>-6.5252</v>
@@ -2395,7 +2395,7 @@
         <v>-3.1151</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.133700000000001</v>
+        <v>-5.133699999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.3204</v>
@@ -2404,13 +2404,13 @@
         <v>7.1868</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6587000000000001</v>
+        <v>1.3561</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9192</v>
+        <v>-1.9191</v>
       </c>
       <c r="U25" t="n">
-        <v>2.578</v>
+        <v>3.2752</v>
       </c>
       <c r="V25" t="n">
         <v>2.9467</v>
